--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Bakery_20260308.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Bakery_20260308.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,27 @@
         <v>79.94</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Shortening - High Ratio</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>94.65000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
